--- a/src/attributions/attributions_ig_traj_113.xlsx
+++ b/src/attributions/attributions_ig_traj_113.xlsx
@@ -1568,46 +1568,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-0.02387994216587988</v>
+        <v>-0.0484860329446872</v>
       </c>
       <c r="B3" t="n">
         <v>-0</v>
       </c>
       <c r="C3" t="n">
-        <v>0.04423836226719257</v>
+        <v>0.09639894652369038</v>
       </c>
       <c r="D3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.3109553807120964</v>
+        <v>-0.06750373816886869</v>
       </c>
       <c r="F3" t="n">
         <v>-0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0.06846436624569116</v>
+        <v>0.07186379493497787</v>
       </c>
       <c r="K3" t="n">
         <v>-0</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0249688642728071</v>
+        <v>0.02552637193683392</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.09454779131188673</v>
+        <v>-0.04260982316417627</v>
       </c>
       <c r="O3" t="n">
         <v>-0</v>
@@ -1619,22 +1619,22 @@
         <v>-0</v>
       </c>
       <c r="R3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.03168151445261891</v>
+        <v>-0.01575767975378287</v>
       </c>
       <c r="T3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.06637150305081928</v>
+        <v>0.02984674814893718</v>
       </c>
       <c r="V3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.159006396158469</v>
+        <v>-0.06096029311639743</v>
       </c>
       <c r="X3" t="n">
         <v>-0</v>
@@ -1646,22 +1646,22 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.1609791011536527</v>
+        <v>0.09979290392507162</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.02361942381452062</v>
+        <v>-0.07002801367296692</v>
       </c>
       <c r="AE3" t="n">
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.02592911007818441</v>
+        <v>-0.06463201463705739</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
@@ -1673,52 +1673,52 @@
         <v>-0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.04876121667008308</v>
+        <v>0.01949289835015325</v>
       </c>
       <c r="AL3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>-0.01343200075943153</v>
+        <v>-0.06303431104943914</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.1958302291719787</v>
+        <v>-0.08115700344499431</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.02022805764024063</v>
+        <v>-0.1020022336225173</v>
       </c>
       <c r="AU3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.1987753885576469</v>
+        <v>0.02685105562453679</v>
       </c>
       <c r="AW3" t="n">
         <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>-0.1560345113198693</v>
+        <v>-0.2929324016138831</v>
       </c>
       <c r="AY3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ3" t="n">
         <v>-0</v>
@@ -1730,19 +1730,19 @@
         <v>-0</v>
       </c>
       <c r="BC3" t="n">
-        <v>-0.01787269212887546</v>
+        <v>-0.01910629759430276</v>
       </c>
       <c r="BD3" t="n">
         <v>-0</v>
       </c>
       <c r="BE3" t="n">
-        <v>-0.05073095867579099</v>
+        <v>0.02061645780526284</v>
       </c>
       <c r="BF3" t="n">
         <v>-0</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0.06857875362670816</v>
+        <v>0.04728329446483807</v>
       </c>
       <c r="BH3" t="n">
         <v>-0</v>
@@ -1754,214 +1754,214 @@
         <v>-0</v>
       </c>
       <c r="BK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.05171459732950769</v>
+        <v>0.06570134257161722</v>
       </c>
       <c r="BM3" t="n">
         <v>0</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.05090091160877816</v>
+        <v>-0.004742598019112254</v>
       </c>
       <c r="BO3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.2048556167741133</v>
+        <v>0.02553592731720253</v>
       </c>
       <c r="BQ3" t="n">
         <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS3" t="n">
         <v>-0</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU3" t="n">
-        <v>-0.1126478609103825</v>
+        <v>-0.1133358570935626</v>
       </c>
       <c r="BV3" t="n">
         <v>0</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.1428211857031447</v>
+        <v>0.1079446506879617</v>
       </c>
       <c r="BX3" t="n">
         <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>-0.1711391198644961</v>
+        <v>-0.1057341613989375</v>
       </c>
       <c r="BZ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA3" t="n">
         <v>-0</v>
       </c>
       <c r="CB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD3" t="n">
-        <v>0.04910369290929716</v>
+        <v>0.06429209490315575</v>
       </c>
       <c r="CE3" t="n">
         <v>0</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.01455701743148143</v>
+        <v>-0.02702252280236079</v>
       </c>
       <c r="CG3" t="n">
         <v>0</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.09469073594687775</v>
+        <v>0.07469186226594246</v>
       </c>
       <c r="CI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK3" t="n">
         <v>-0</v>
       </c>
       <c r="CL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM3" t="n">
-        <v>0.004376270183749745</v>
+        <v>-0.03838746712629156</v>
       </c>
       <c r="CN3" t="n">
         <v>-0</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.05915602807276087</v>
+        <v>0.0005648080097773263</v>
       </c>
       <c r="CP3" t="n">
         <v>0</v>
       </c>
       <c r="CQ3" t="n">
-        <v>-0.2029922949848715</v>
+        <v>-0.03301877197857803</v>
       </c>
       <c r="CR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS3" t="n">
         <v>0</v>
       </c>
       <c r="CT3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV3" t="n">
-        <v>0.05461946601964401</v>
+        <v>0.05177993405038094</v>
       </c>
       <c r="CW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CX3" t="n">
-        <v>0.002872232128648577</v>
+        <v>-0.05081347222990939</v>
       </c>
       <c r="CY3" t="n">
         <v>-0</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.0792547718855332</v>
+        <v>0.02877716813178187</v>
       </c>
       <c r="DA3" t="n">
         <v>-0</v>
       </c>
       <c r="DB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC3" t="n">
         <v>0</v>
       </c>
       <c r="DD3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.008211882139525622</v>
+        <v>0.04498489452974118</v>
       </c>
       <c r="DF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DG3" t="n">
-        <v>0.0001091684163302863</v>
+        <v>0.0002834923963718497</v>
       </c>
       <c r="DH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.09264915568442901</v>
+        <v>0.1508451871207387</v>
       </c>
       <c r="DJ3" t="n">
         <v>-0</v>
       </c>
       <c r="DK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM3" t="n">
         <v>0</v>
       </c>
       <c r="DN3" t="n">
-        <v>-0.07263475966045466</v>
+        <v>0.09661820096608986</v>
       </c>
       <c r="DO3" t="n">
         <v>0</v>
       </c>
       <c r="DP3" t="n">
-        <v>0.005952118578333238</v>
+        <v>0.0476532238748771</v>
       </c>
       <c r="DQ3" t="n">
         <v>0</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.1121966653471687</v>
+        <v>-0.1195093753926023</v>
       </c>
       <c r="DS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU3" t="n">
         <v>-0</v>
       </c>
       <c r="DV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW3" t="n">
-        <v>-0.08886121172554554</v>
+        <v>0.01495371574373207</v>
       </c>
       <c r="DX3" t="n">
         <v>0</v>
       </c>
       <c r="DY3" t="n">
-        <v>0.04107319523280009</v>
+        <v>0.1708569327019817</v>
       </c>
       <c r="DZ3" t="n">
         <v>0</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.0411325746166283</v>
+        <v>-0.1168235215429266</v>
       </c>
       <c r="EB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC3" t="n">
         <v>-0</v>
@@ -1970,25 +1970,25 @@
         <v>0</v>
       </c>
       <c r="EE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF3" t="n">
-        <v>0.03911675225022222</v>
+        <v>0.04631911944123258</v>
       </c>
       <c r="EG3" t="n">
         <v>0</v>
       </c>
       <c r="EH3" t="n">
-        <v>-0.009583745026880143</v>
+        <v>0.01238917840760085</v>
       </c>
       <c r="EI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ3" t="n">
-        <v>-0.003475514962451935</v>
+        <v>0.07165492441231455</v>
       </c>
       <c r="EK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL3" t="n">
         <v>0</v>
@@ -1997,28 +1997,28 @@
         <v>-0</v>
       </c>
       <c r="EN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO3" t="n">
-        <v>0.0263667538573165</v>
+        <v>0.01525098544167433</v>
       </c>
       <c r="EP3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0.03379367013724691</v>
+        <v>-0.01305045365134333</v>
       </c>
       <c r="ER3" t="n">
         <v>0</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.009559720233026469</v>
+        <v>0.09243970820415208</v>
       </c>
       <c r="ET3" t="n">
         <v>0</v>
       </c>
       <c r="EU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV3" t="n">
         <v>0</v>
@@ -2027,52 +2027,52 @@
         <v>0</v>
       </c>
       <c r="EX3" t="n">
-        <v>0.05834644353766964</v>
+        <v>0.04784258987389636</v>
       </c>
       <c r="EY3" t="n">
         <v>0</v>
       </c>
       <c r="EZ3" t="n">
-        <v>0.00707244717498297</v>
+        <v>-0.04607094374195719</v>
       </c>
       <c r="FA3" t="n">
         <v>0</v>
       </c>
       <c r="FB3" t="n">
-        <v>0.07082153085388666</v>
+        <v>0.0470597542319963</v>
       </c>
       <c r="FC3" t="n">
         <v>0</v>
       </c>
       <c r="FD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE3" t="n">
         <v>-0</v>
       </c>
       <c r="FF3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG3" t="n">
-        <v>0.08431965690033606</v>
+        <v>0.1956393082620361</v>
       </c>
       <c r="FH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FI3" t="n">
-        <v>0.03236223307667872</v>
+        <v>0.03069369887132344</v>
       </c>
       <c r="FJ3" t="n">
         <v>0</v>
       </c>
       <c r="FK3" t="n">
-        <v>0.1215425241916863</v>
+        <v>-0.01486215479456418</v>
       </c>
       <c r="FL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN3" t="n">
         <v>0</v>
@@ -2081,19 +2081,19 @@
         <v>0</v>
       </c>
       <c r="FP3" t="n">
-        <v>0.1135710486671017</v>
+        <v>0.1446803224772242</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FR3" t="n">
-        <v>-4.79852101098104e-05</v>
+        <v>0.001902585757404995</v>
       </c>
       <c r="FS3" t="n">
         <v>0</v>
       </c>
       <c r="FT3" t="n">
-        <v>0.005309427575977969</v>
+        <v>0.006981715534439817</v>
       </c>
       <c r="FU3" t="n">
         <v>0</v>
@@ -2105,31 +2105,31 @@
         <v>-0</v>
       </c>
       <c r="FX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY3" t="n">
-        <v>0.06555240619387745</v>
+        <v>0.1600746845603644</v>
       </c>
       <c r="FZ3" t="n">
         <v>-0</v>
       </c>
       <c r="GA3" t="n">
-        <v>0.1164009954721865</v>
+        <v>-0.003841441860856897</v>
       </c>
       <c r="GB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC3" t="n">
         <v>-0</v>
       </c>
       <c r="GD3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE3" t="n">
         <v>0</v>
       </c>
       <c r="GF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG3" t="n">
         <v>0</v>
@@ -2140,16 +2140,16 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>0.2471629162950395</v>
+        <v>0.179613926279966</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.05469702287120912</v>
+        <v>-0.05034353505131715</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.04568833610068638</v>
+        <v>-0.03469737555791962</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -2161,25 +2161,25 @@
         <v>-0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.09538591272888454</v>
+        <v>0.1028784747415487</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0.02998375722540975</v>
+        <v>0.03545148062881524</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.02983823272383012</v>
+        <v>-0.01664562541376794</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P4" t="n">
         <v>-0</v>
@@ -2188,76 +2188,76 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1173243944990684</v>
+        <v>0.03249533076362399</v>
       </c>
       <c r="U4" t="n">
         <v>-0</v>
       </c>
       <c r="V4" t="n">
-        <v>0.03846835999169186</v>
+        <v>-0.02812006471456355</v>
       </c>
       <c r="W4" t="n">
-        <v>0.03425476681290692</v>
+        <v>-0.02463001854279404</v>
       </c>
       <c r="X4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
         <v>-0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.0516774881833913</v>
+        <v>-0.0047382950716011</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0.02742806673338002</v>
+        <v>-0.06859742650687282</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.03625930910709115</v>
+        <v>-0.06880775091043745</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
         <v>-0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.05331992868024171</v>
+        <v>0.0927227839224954</v>
       </c>
       <c r="AM4" t="n">
         <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>-0.03876899621650962</v>
+        <v>-0.03851878072047424</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0.01728952481418551</v>
+        <v>0.05171186385550246</v>
       </c>
       <c r="AP4" t="n">
         <v>0</v>
@@ -2266,7 +2266,7 @@
         <v>0</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS4" t="n">
         <v>0</v>
@@ -2275,25 +2275,25 @@
         <v>-0</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.4311595110618587</v>
+        <v>0.2587132167288359</v>
       </c>
       <c r="AV4" t="n">
         <v>-0</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.01005438750606607</v>
+        <v>-0.06306808926543234</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.1910853811234853</v>
+        <v>-0.1045146044688246</v>
       </c>
       <c r="AY4" t="n">
         <v>-0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="n">
         <v>-0</v>
@@ -2302,16 +2302,16 @@
         <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.01160368163996225</v>
+        <v>-0.01287365941134037</v>
       </c>
       <c r="BE4" t="n">
         <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>-0.04531425025126586</v>
+        <v>-0.01353966062526527</v>
       </c>
       <c r="BG4" t="n">
-        <v>-0.07481665085510228</v>
+        <v>-0.01507798625436327</v>
       </c>
       <c r="BH4" t="n">
         <v>0</v>
@@ -2320,7 +2320,7 @@
         <v>-0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK4" t="n">
         <v>0</v>
@@ -2329,22 +2329,22 @@
         <v>-0</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.04617740060078838</v>
+        <v>-0.01163268781803427</v>
       </c>
       <c r="BN4" t="n">
         <v>-0</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.0984193156270277</v>
+        <v>0.02605631235070431</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.0163837743719536</v>
+        <v>0.06666821764109841</v>
       </c>
       <c r="BQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
         <v>-0</v>
@@ -2356,25 +2356,25 @@
         <v>-0</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.2003815959951325</v>
+        <v>0.1562485730195496</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.01126993492628888</v>
+        <v>-0.04058479523126678</v>
       </c>
       <c r="BY4" t="n">
-        <v>-0.007273794442301349</v>
+        <v>-0.01417392364819943</v>
       </c>
       <c r="BZ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA4" t="n">
         <v>-0</v>
       </c>
       <c r="CB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC4" t="n">
         <v>0</v>
@@ -2383,46 +2383,46 @@
         <v>-0</v>
       </c>
       <c r="CE4" t="n">
-        <v>-0.06788075253471304</v>
+        <v>-0.09187620370055827</v>
       </c>
       <c r="CF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.01221295663051582</v>
+        <v>0.0732379777153926</v>
       </c>
       <c r="CH4" t="n">
-        <v>-0.02552130251395173</v>
+        <v>0.01011202359175027</v>
       </c>
       <c r="CI4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK4" t="n">
         <v>0</v>
       </c>
       <c r="CL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM4" t="n">
         <v>0</v>
       </c>
       <c r="CN4" t="n">
-        <v>-0.04029368601245266</v>
+        <v>-0.07512360140673538</v>
       </c>
       <c r="CO4" t="n">
         <v>-0</v>
       </c>
       <c r="CP4" t="n">
-        <v>-0.1072821478091828</v>
+        <v>0.09703235556920622</v>
       </c>
       <c r="CQ4" t="n">
-        <v>-0.1650013860501659</v>
+        <v>0.0273455648687515</v>
       </c>
       <c r="CR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS4" t="n">
         <v>-0</v>
@@ -2437,49 +2437,49 @@
         <v>0</v>
       </c>
       <c r="CW4" t="n">
-        <v>-0.05151957546532296</v>
+        <v>-0.09793489226610176</v>
       </c>
       <c r="CX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.04088214664527261</v>
+        <v>0.08147152120120188</v>
       </c>
       <c r="CZ4" t="n">
-        <v>-0.0196630974626667</v>
+        <v>0.01739032326093544</v>
       </c>
       <c r="DA4" t="n">
         <v>0</v>
       </c>
       <c r="DB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>-0.075032676311462</v>
+        <v>-0.03970338374401541</v>
       </c>
       <c r="DG4" t="n">
         <v>0</v>
       </c>
       <c r="DH4" t="n">
-        <v>-0.005499403396417012</v>
+        <v>-0.005140527971063469</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.0002965499564725607</v>
+        <v>0.00138992653784085</v>
       </c>
       <c r="DJ4" t="n">
         <v>-0</v>
       </c>
       <c r="DK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL4" t="n">
         <v>0</v>
@@ -2491,25 +2491,25 @@
         <v>-0</v>
       </c>
       <c r="DO4" t="n">
-        <v>-0.06700831518893315</v>
+        <v>-0.07158779623042377</v>
       </c>
       <c r="DP4" t="n">
         <v>-0</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.03261513809258627</v>
+        <v>0.03293490492429371</v>
       </c>
       <c r="DR4" t="n">
-        <v>-0.01277930582802048</v>
+        <v>-0.03555807033842784</v>
       </c>
       <c r="DS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT4" t="n">
         <v>-0</v>
       </c>
       <c r="DU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV4" t="n">
         <v>0</v>
@@ -2518,19 +2518,19 @@
         <v>-0</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.06202172268184585</v>
+        <v>0.01106737165236916</v>
       </c>
       <c r="DY4" t="n">
         <v>0</v>
       </c>
       <c r="DZ4" t="n">
-        <v>-0.069094883220001</v>
+        <v>0.04191390917615634</v>
       </c>
       <c r="EA4" t="n">
-        <v>-0.02010133722901953</v>
+        <v>-0.01646559624069333</v>
       </c>
       <c r="EB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC4" t="n">
         <v>-0</v>
@@ -2539,31 +2539,31 @@
         <v>0</v>
       </c>
       <c r="EE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF4" t="n">
         <v>0</v>
       </c>
       <c r="EG4" t="n">
-        <v>-0.03622736817609308</v>
+        <v>-0.06085316867712939</v>
       </c>
       <c r="EH4" t="n">
         <v>-0</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.08013562621035659</v>
+        <v>0.06463082898448158</v>
       </c>
       <c r="EJ4" t="n">
-        <v>-0.003958419594526416</v>
+        <v>0.0190345100516935</v>
       </c>
       <c r="EK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN4" t="n">
         <v>-0</v>
@@ -2572,73 +2572,73 @@
         <v>0</v>
       </c>
       <c r="EP4" t="n">
-        <v>-0.03739370156106853</v>
+        <v>-0.0508013778402995</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER4" t="n">
-        <v>-0.03677115146384054</v>
+        <v>-0.03997872678827779</v>
       </c>
       <c r="ES4" t="n">
-        <v>-0.02209716745781563</v>
+        <v>-0.00164039116810361</v>
       </c>
       <c r="ET4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV4" t="n">
         <v>0</v>
       </c>
       <c r="EW4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX4" t="n">
         <v>-0</v>
       </c>
       <c r="EY4" t="n">
-        <v>-0.05953961508588553</v>
+        <v>-0.1056729932039917</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA4" t="n">
-        <v>0.01995281555780826</v>
+        <v>0.07824907363117149</v>
       </c>
       <c r="FB4" t="n">
-        <v>-0.03904768698970316</v>
+        <v>0.008688751551515685</v>
       </c>
       <c r="FC4" t="n">
         <v>-0</v>
       </c>
       <c r="FD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH4" t="n">
-        <v>0.03266067008926511</v>
+        <v>-0.05887692500327998</v>
       </c>
       <c r="FI4" t="n">
         <v>-0</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0.0472570126832309</v>
+        <v>0.02547145398708247</v>
       </c>
       <c r="FK4" t="n">
-        <v>-0.01900440967385729</v>
+        <v>0.008384617245649871</v>
       </c>
       <c r="FL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM4" t="n">
         <v>0</v>
@@ -2647,28 +2647,28 @@
         <v>-0</v>
       </c>
       <c r="FO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP4" t="n">
         <v>-0</v>
       </c>
       <c r="FQ4" t="n">
-        <v>0.002565098676272511</v>
+        <v>0.0003013947114163567</v>
       </c>
       <c r="FR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS4" t="n">
-        <v>0.002366605078880382</v>
+        <v>0.1132583219897656</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.0006560343917926179</v>
+        <v>-0.0008031163961664595</v>
       </c>
       <c r="FU4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW4" t="n">
         <v>0</v>
@@ -2677,31 +2677,31 @@
         <v>0</v>
       </c>
       <c r="FY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ4" t="n">
-        <v>-0.003915886601314767</v>
+        <v>-0.07255453999779005</v>
       </c>
       <c r="GA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB4" t="n">
-        <v>-0.02239254671888356</v>
+        <v>0.02505770036007453</v>
       </c>
       <c r="GC4" t="n">
         <v>0</v>
       </c>
       <c r="GD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE4" t="n">
         <v>-0</v>
       </c>
       <c r="GF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -2709,25 +2709,25 @@
         <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.03800069404876592</v>
+        <v>0.4658288791637943</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.03525535501985389</v>
+        <v>0.09539129858271411</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.02598064096380983</v>
+        <v>-0.2514223255475945</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -2736,34 +2736,34 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.009398298371234303</v>
+        <v>0.3174598445301431</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.01825425781421329</v>
+        <v>-0.01648271762813879</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.003221702859386785</v>
+        <v>-0.03592397253167934</v>
       </c>
       <c r="P5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0009934357237345005</v>
+        <v>0.1520991252960944</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -2772,52 +2772,52 @@
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.01004419101084892</v>
+        <v>-0.1655515841563074</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01381315790261587</v>
+        <v>0.01841025462593699</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.01768276043130143</v>
+        <v>-0.01458217210783936</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.01153433419562587</v>
+        <v>-0.3359350782351406</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.0130075754624334</v>
+        <v>-0.001331439439212522</v>
       </c>
       <c r="AH5" t="n">
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.007541875633067159</v>
+        <v>0.1377645689576549</v>
       </c>
       <c r="AM5" t="n">
         <v>0</v>
@@ -2826,37 +2826,37 @@
         <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.01406023852465389</v>
+        <v>0.1090607529024117</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.0043952615920624</v>
+        <v>-0.07830091298983666</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS5" t="n">
         <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.05223954603005503</v>
+        <v>0.7279044575090516</v>
       </c>
       <c r="AV5" t="n">
         <v>0</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.03975044151416369</v>
+        <v>-0.2005969846102663</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.01854721890132405</v>
+        <v>-0.2758158297135391</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
@@ -2871,52 +2871,52 @@
         <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.01302395278663267</v>
+        <v>0.02573793376450508</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.01270479675105719</v>
+        <v>-0.05164727014577424</v>
       </c>
       <c r="BH5" t="n">
-        <v>-0.00789208275421498</v>
+        <v>-0.0720697093707921</v>
       </c>
       <c r="BI5" t="n">
         <v>-0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK5" t="n">
         <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.0355178562122809</v>
+        <v>0.02409002101985082</v>
       </c>
       <c r="BN5" t="n">
         <v>0</v>
       </c>
       <c r="BO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.0169657445136474</v>
+        <v>0.1149153901373274</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.006094671662352475</v>
+        <v>0.1364306819583253</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT5" t="n">
         <v>0</v>
@@ -2925,7 +2925,7 @@
         <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.01720140191143617</v>
+        <v>0.4848383679283297</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
@@ -2934,37 +2934,37 @@
         <v>0</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.01886271329900989</v>
+        <v>0.03120988546473544</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.003989040392572921</v>
+        <v>-0.1422820699556171</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD5" t="n">
         <v>-0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.005459350455923218</v>
+        <v>-0.2155001821624479</v>
       </c>
       <c r="CF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG5" t="n">
         <v>0</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.01378787856393345</v>
+        <v>-0.07608431013970987</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.01185848844627145</v>
+        <v>0.1683194903943293</v>
       </c>
       <c r="CJ5" t="n">
         <v>0</v>
@@ -2976,52 +2976,52 @@
         <v>-0</v>
       </c>
       <c r="CM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN5" t="n">
-        <v>-0.0011103742081056</v>
+        <v>-0.3036006836430674</v>
       </c>
       <c r="CO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP5" t="n">
         <v>-0</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.00477397516967024</v>
+        <v>0.1120730367037724</v>
       </c>
       <c r="CR5" t="n">
-        <v>-0.006500131911404337</v>
+        <v>0.08976632366626339</v>
       </c>
       <c r="CS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT5" t="n">
         <v>0</v>
       </c>
       <c r="CU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV5" t="n">
         <v>0</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.0004983075013660408</v>
+        <v>-0.2031971354146812</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY5" t="n">
         <v>-0</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.0136002058158752</v>
+        <v>-0.07408322012456615</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.01441947642440513</v>
+        <v>0.1664859229743834</v>
       </c>
       <c r="DB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC5" t="n">
         <v>0</v>
@@ -3033,52 +3033,52 @@
         <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.009193534806671264</v>
+        <v>-0.0856855406486601</v>
       </c>
       <c r="DG5" t="n">
         <v>-0</v>
       </c>
       <c r="DH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.01008403638378884</v>
+        <v>-0.1794785156275064</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.003180356416458649</v>
+        <v>0.04390568558990539</v>
       </c>
       <c r="DK5" t="n">
         <v>0</v>
       </c>
       <c r="DL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN5" t="n">
         <v>-0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.01061448000570377</v>
+        <v>-0.1520530219784929</v>
       </c>
       <c r="DP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ5" t="n">
         <v>0</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.01980225903655083</v>
+        <v>0.03930691693330237</v>
       </c>
       <c r="DS5" t="n">
-        <v>-0.01419298494374579</v>
+        <v>0.06600986882585952</v>
       </c>
       <c r="DT5" t="n">
         <v>-0</v>
       </c>
       <c r="DU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV5" t="n">
         <v>-0</v>
@@ -3087,25 +3087,25 @@
         <v>-0</v>
       </c>
       <c r="DX5" t="n">
-        <v>-0.01333383318623554</v>
+        <v>-0.05806581439930237</v>
       </c>
       <c r="DY5" t="n">
         <v>0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.01637088420134843</v>
+        <v>0.05813899168975464</v>
       </c>
       <c r="EB5" t="n">
-        <v>-0.003604206115618716</v>
+        <v>0.1810812130836255</v>
       </c>
       <c r="EC5" t="n">
         <v>-0</v>
       </c>
       <c r="ED5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE5" t="n">
         <v>-0</v>
@@ -3114,34 +3114,34 @@
         <v>-0</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.00195624052363005</v>
+        <v>-0.09026285477251203</v>
       </c>
       <c r="EH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI5" t="n">
         <v>0</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.001086180512904701</v>
+        <v>-0.1527758058836197</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.005077354019620811</v>
+        <v>0.0372598100697265</v>
       </c>
       <c r="EL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.010211914069912</v>
+        <v>-0.08718082553016114</v>
       </c>
       <c r="EQ5" t="n">
         <v>-0</v>
@@ -3150,25 +3150,25 @@
         <v>0</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.0126764229048419</v>
+        <v>-0.2393009002463676</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.01241779012679581</v>
+        <v>0.1532519427205795</v>
       </c>
       <c r="EU5" t="n">
         <v>0</v>
       </c>
       <c r="EV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX5" t="n">
         <v>-0</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.003645584913446339</v>
+        <v>-0.2217208731039857</v>
       </c>
       <c r="EZ5" t="n">
         <v>-0</v>
@@ -3177,10 +3177,10 @@
         <v>0</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.01211168436949582</v>
+        <v>-0.1237861966690678</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.01404402191285117</v>
+        <v>0.1364327435048612</v>
       </c>
       <c r="FD5" t="n">
         <v>0</v>
@@ -3195,34 +3195,34 @@
         <v>0</v>
       </c>
       <c r="FH5" t="n">
-        <v>-0.01722395715803254</v>
+        <v>-0.2706646563481678</v>
       </c>
       <c r="FI5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ5" t="n">
         <v>-0</v>
       </c>
       <c r="FK5" t="n">
-        <v>-0.022694903750061</v>
+        <v>0.0804312533074989</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.01030914603037229</v>
+        <v>0.1919210206715879</v>
       </c>
       <c r="FM5" t="n">
         <v>0</v>
       </c>
       <c r="FN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO5" t="n">
         <v>0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.002013209561533012</v>
+        <v>0.03071416604046985</v>
       </c>
       <c r="FR5" t="n">
         <v>0</v>
@@ -3231,25 +3231,25 @@
         <v>-0</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.001026481503808376</v>
+        <v>0.004461095422962756</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.02569650261030959</v>
+        <v>-0.08550858668089237</v>
       </c>
       <c r="FV5" t="n">
         <v>-0</v>
       </c>
       <c r="FW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>-0.0187176415911546</v>
+        <v>-0.08506618556027554</v>
       </c>
       <c r="GA5" t="n">
         <v>0</v>
@@ -3261,7 +3261,7 @@
         <v>-0</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.0007302476132244867</v>
+        <v>0.1106375533844419</v>
       </c>
       <c r="GE5" t="n">
         <v>0</v>
@@ -3847,16 +3847,16 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.3628568623304991</v>
+        <v>0.2666757538867179</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.146169585356274</v>
+        <v>-0.1248747206144348</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.06313656389089674</v>
+        <v>-0.04244250975019626</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -3868,112 +3868,112 @@
         <v>-0</v>
       </c>
       <c r="I7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1926903477043752</v>
+        <v>0.2162401189042749</v>
       </c>
       <c r="L7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.03893427283731483</v>
+        <v>-0.04569722565034948</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.06744548216467626</v>
+        <v>-0.05858302693231487</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P7" t="n">
         <v>-0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1115023178337828</v>
+        <v>0.05759985142164072</v>
       </c>
       <c r="U7" t="n">
         <v>-0</v>
       </c>
       <c r="V7" t="n">
-        <v>0.01343832020718358</v>
+        <v>-0.04618226644058112</v>
       </c>
       <c r="W7" t="n">
-        <v>0.01676504603010602</v>
+        <v>-0.05944266662444879</v>
       </c>
       <c r="X7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
         <v>-0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.07640701118550346</v>
+        <v>-0.04374090749170491</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.03639615647119099</v>
+        <v>-0.07089903720601806</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.01615937067061281</v>
+        <v>-0.1188135612780875</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>-0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.06016406515526213</v>
+        <v>0.1236760347903511</v>
       </c>
       <c r="AM7" t="n">
         <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0.03904864141533908</v>
+        <v>-0.06320362186545046</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.03563472912575486</v>
+        <v>0.03780119801061455</v>
       </c>
       <c r="AP7" t="n">
         <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS7" t="n">
         <v>0</v>
@@ -3982,25 +3982,25 @@
         <v>-0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.4798287479721036</v>
+        <v>0.3282603031197152</v>
       </c>
       <c r="AV7" t="n">
         <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0.009929144767735935</v>
+        <v>-0.1173735229305672</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.1843170920120845</v>
+        <v>-0.1926773940262264</v>
       </c>
       <c r="AY7" t="n">
         <v>-0</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
         <v>-0</v>
@@ -4009,16 +4009,16 @@
         <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.02075468129646752</v>
+        <v>-0.03957842036625792</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>-0.07027882764688889</v>
+        <v>-0.01624857713512113</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.1180693354847731</v>
+        <v>-0.01617883109984566</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
@@ -4027,7 +4027,7 @@
         <v>-0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK7" t="n">
         <v>0</v>
@@ -4036,22 +4036,22 @@
         <v>-0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.05964858000087809</v>
+        <v>0.008406382362853905</v>
       </c>
       <c r="BN7" t="n">
         <v>-0</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.1067338090295818</v>
+        <v>0.04519502969816216</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.02983280349139278</v>
+        <v>0.06424133625673197</v>
       </c>
       <c r="BQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
         <v>-0</v>
@@ -4063,25 +4063,25 @@
         <v>-0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.2164832837473619</v>
+        <v>0.206619985174872</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX7" t="n">
-        <v>-0.002559279956250925</v>
+        <v>-0.04744138606931481</v>
       </c>
       <c r="BY7" t="n">
-        <v>-0.003921618342454592</v>
+        <v>-0.05385042008187734</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA7" t="n">
         <v>-0</v>
       </c>
       <c r="CB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC7" t="n">
         <v>0</v>
@@ -4090,46 +4090,46 @@
         <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.08260671763443521</v>
+        <v>-0.1098414919046652</v>
       </c>
       <c r="CF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.01953831011302305</v>
+        <v>0.1112662401740591</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.02768183788427177</v>
+        <v>0.01642856362133255</v>
       </c>
       <c r="CI7" t="n">
         <v>-0</v>
       </c>
       <c r="CJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK7" t="n">
         <v>0</v>
       </c>
       <c r="CL7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM7" t="n">
         <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>-0.01707146763427918</v>
+        <v>-0.0766797364410452</v>
       </c>
       <c r="CO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP7" t="n">
-        <v>-0.1377049822536325</v>
+        <v>0.173673633046221</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.1631174528904515</v>
+        <v>0.07199079180983171</v>
       </c>
       <c r="CR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS7" t="n">
         <v>-0</v>
@@ -4144,49 +4144,49 @@
         <v>0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.06650482891969581</v>
+        <v>-0.1096469993970576</v>
       </c>
       <c r="CX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.04865483459184863</v>
+        <v>0.1229487850804609</v>
       </c>
       <c r="CZ7" t="n">
-        <v>-0.023915946017714</v>
+        <v>0.02214829854786089</v>
       </c>
       <c r="DA7" t="n">
         <v>0</v>
       </c>
       <c r="DB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.03683277088511744</v>
+        <v>-0.04349874264067896</v>
       </c>
       <c r="DG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH7" t="n">
-        <v>-0.007610558223505482</v>
+        <v>-0.008836380326740348</v>
       </c>
       <c r="DI7" t="n">
-        <v>-1.787153472262701e-05</v>
+        <v>-0.01574010340486596</v>
       </c>
       <c r="DJ7" t="n">
         <v>-0</v>
       </c>
       <c r="DK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL7" t="n">
         <v>0</v>
@@ -4198,19 +4198,19 @@
         <v>-0</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0.08465028139256769</v>
+        <v>-0.07011684266698995</v>
       </c>
       <c r="DP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.03651334858419486</v>
+        <v>0.01802154020605308</v>
       </c>
       <c r="DR7" t="n">
-        <v>-0.0135484152780193</v>
+        <v>-0.03752679626675066</v>
       </c>
       <c r="DS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT7" t="n">
         <v>-0</v>
@@ -4225,19 +4225,19 @@
         <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.04379611688632389</v>
+        <v>0.0176175305329667</v>
       </c>
       <c r="DY7" t="n">
         <v>0</v>
       </c>
       <c r="DZ7" t="n">
-        <v>-0.06549114783718055</v>
+        <v>0.03606809042608072</v>
       </c>
       <c r="EA7" t="n">
-        <v>-0.01295206000405353</v>
+        <v>-0.01315285799440456</v>
       </c>
       <c r="EB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC7" t="n">
         <v>-0</v>
@@ -4246,55 +4246,55 @@
         <v>0</v>
       </c>
       <c r="EE7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF7" t="n">
         <v>0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.02358203772215772</v>
+        <v>-0.07235839968642574</v>
       </c>
       <c r="EH7" t="n">
         <v>-0</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.07514161302910161</v>
+        <v>0.1130991987956857</v>
       </c>
       <c r="EJ7" t="n">
-        <v>-0.00573341950974149</v>
+        <v>0.01106594180649839</v>
       </c>
       <c r="EK7" t="n">
         <v>-0</v>
       </c>
       <c r="EL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN7" t="n">
         <v>-0</v>
       </c>
       <c r="EO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.05096180898064721</v>
+        <v>-0.0590752010890173</v>
       </c>
       <c r="EQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER7" t="n">
-        <v>-0.03044255610259173</v>
+        <v>-0.09887229497449304</v>
       </c>
       <c r="ES7" t="n">
-        <v>-0.03743933986481726</v>
+        <v>0.005214707683499402</v>
       </c>
       <c r="ET7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV7" t="n">
         <v>0</v>
@@ -4306,46 +4306,46 @@
         <v>-0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.07216906886292482</v>
+        <v>-0.1232390617416138</v>
       </c>
       <c r="EZ7" t="n">
         <v>-0</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.03104807603484139</v>
+        <v>0.1199789626652268</v>
       </c>
       <c r="FB7" t="n">
-        <v>-0.03061752292463377</v>
+        <v>0.007763965587995482</v>
       </c>
       <c r="FC7" t="n">
         <v>-0</v>
       </c>
       <c r="FD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH7" t="n">
-        <v>0.01364514381003121</v>
+        <v>-0.06910573841609469</v>
       </c>
       <c r="FI7" t="n">
         <v>-0</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.0668984267615525</v>
+        <v>0.05697224188882624</v>
       </c>
       <c r="FK7" t="n">
-        <v>0.002344268781006869</v>
+        <v>-0.001430733176898094</v>
       </c>
       <c r="FL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM7" t="n">
         <v>0</v>
@@ -4354,25 +4354,25 @@
         <v>-0</v>
       </c>
       <c r="FO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>0.007205682496229892</v>
+        <v>0.003203458454476553</v>
       </c>
       <c r="FR7" t="n">
         <v>0</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.01154021451688915</v>
+        <v>0.1386525475746518</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.01520853648156043</v>
+        <v>-0.009616275443767957</v>
       </c>
       <c r="FU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV7" t="n">
         <v>-0</v>
@@ -4384,31 +4384,31 @@
         <v>0</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>-0.007080909133213353</v>
+        <v>-0.09162101248312757</v>
       </c>
       <c r="GA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB7" t="n">
-        <v>-0.01993619953328231</v>
+        <v>0.05680922125362325</v>
       </c>
       <c r="GC7" t="n">
         <v>0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE7" t="n">
         <v>-0</v>
       </c>
       <c r="GF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -4985,7 +4985,7 @@
         <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>0.07744483187820088</v>
+        <v>0.5368694544595716</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -4994,25 +4994,25 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.02052011562308737</v>
+        <v>-0.01682711315342352</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.02923739364361466</v>
+        <v>-0.246617487777578</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.02832709217380087</v>
+        <v>0.488166968450188</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -5021,25 +5021,25 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.02200074653882897</v>
+        <v>-0.1424722681284992</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.001859796386424758</v>
+        <v>-0.01349645022918469</v>
       </c>
       <c r="P9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0005248244636739394</v>
+        <v>0.1754823728846748</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -5048,52 +5048,52 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.00206406976684389</v>
+        <v>-0.03171854806080462</v>
       </c>
       <c r="X9" t="n">
-        <v>0.01931958833985734</v>
+        <v>0.04468702126043426</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB9" t="n">
         <v>-0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.02056071705881227</v>
+        <v>-0.04512673787087779</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.02962827044498503</v>
+        <v>-0.3061552350978539</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.00801715599269732</v>
+        <v>0.07790403999769709</v>
       </c>
       <c r="AH9" t="n">
         <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.01531798765251417</v>
+        <v>0.1934952834415616</v>
       </c>
       <c r="AM9" t="n">
         <v>0</v>
@@ -5102,52 +5102,52 @@
         <v>0</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.005895422950981678</v>
+        <v>0.04254037621148946</v>
       </c>
       <c r="AP9" t="n">
-        <v>-0.009136129347727315</v>
+        <v>-0.1269046840430404</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS9" t="n">
         <v>0</v>
       </c>
       <c r="AT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.08577267525368108</v>
+        <v>0.7467802428559447</v>
       </c>
       <c r="AV9" t="n">
         <v>0</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX9" t="n">
-        <v>-0.005990256470498711</v>
+        <v>-0.2914119549316862</v>
       </c>
       <c r="AY9" t="n">
-        <v>-0.01577541007957426</v>
+        <v>-0.3249643771150122</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.01767188507245903</v>
+        <v>-0.04129160947729123</v>
       </c>
       <c r="BE9" t="n">
         <v>0</v>
@@ -5156,25 +5156,25 @@
         <v>0</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.02217455562090941</v>
+        <v>-0.1335841114682876</v>
       </c>
       <c r="BH9" t="n">
-        <v>-0.007067293590851021</v>
+        <v>-0.04443645144821746</v>
       </c>
       <c r="BI9" t="n">
         <v>-0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK9" t="n">
         <v>0</v>
       </c>
       <c r="BL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.03079723203971411</v>
+        <v>0.04513920441290224</v>
       </c>
       <c r="BN9" t="n">
         <v>-0</v>
@@ -5183,13 +5183,13 @@
         <v>-0</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.02464894714924912</v>
+        <v>0.158405074288219</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.007876111145537214</v>
+        <v>0.1288036443415564</v>
       </c>
       <c r="BR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS9" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
         <v>-0</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.02940903793842699</v>
+        <v>0.4902818260886755</v>
       </c>
       <c r="BW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX9" t="n">
         <v>0</v>
       </c>
       <c r="BY9" t="n">
-        <v>-0.01418787814576417</v>
+        <v>-0.00340967394489678</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.0175861420060917</v>
+        <v>-0.1092468957173351</v>
       </c>
       <c r="CA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB9" t="n">
         <v>-0</v>
@@ -5228,61 +5228,61 @@
         <v>-0</v>
       </c>
       <c r="CE9" t="n">
-        <v>-0.008029861343165799</v>
+        <v>-0.207036898552625</v>
       </c>
       <c r="CF9" t="n">
         <v>-0</v>
       </c>
       <c r="CG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.000766355765171948</v>
+        <v>0.0139639932441716</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.01372345991941326</v>
+        <v>0.1359297346191318</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK9" t="n">
         <v>0</v>
       </c>
       <c r="CL9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.009772799567255568</v>
+        <v>-0.2776536445797544</v>
       </c>
       <c r="CO9" t="n">
         <v>0</v>
       </c>
       <c r="CP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.004454598038388153</v>
+        <v>0.3251756739320048</v>
       </c>
       <c r="CR9" t="n">
-        <v>-0.03135060251938951</v>
+        <v>0.005668914140119155</v>
       </c>
       <c r="CS9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV9" t="n">
         <v>0</v>
       </c>
       <c r="CW9" t="n">
-        <v>-0.003397145499693057</v>
+        <v>-0.1884474724904113</v>
       </c>
       <c r="CX9" t="n">
         <v>0</v>
@@ -5291,67 +5291,67 @@
         <v>0</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.001634401229548923</v>
+        <v>0.02584827816152965</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.01639660760330382</v>
+        <v>0.1473183570108684</v>
       </c>
       <c r="DB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD9" t="n">
         <v>0</v>
       </c>
       <c r="DE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.002220323475479821</v>
+        <v>-0.1834783003065364</v>
       </c>
       <c r="DG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.02692631920144412</v>
+        <v>-0.1479671494948158</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.01352554270227042</v>
+        <v>0.152859999740179</v>
       </c>
       <c r="DK9" t="n">
         <v>0</v>
       </c>
       <c r="DL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN9" t="n">
         <v>-0</v>
       </c>
       <c r="DO9" t="n">
-        <v>-0.008953095262925112</v>
+        <v>-0.1479068666017294</v>
       </c>
       <c r="DP9" t="n">
         <v>-0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.0160937916607804</v>
+        <v>0.009270530592286396</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.00707552574411012</v>
+        <v>0.03196967697249662</v>
       </c>
       <c r="DT9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU9" t="n">
         <v>-0</v>
@@ -5363,25 +5363,25 @@
         <v>-0</v>
       </c>
       <c r="DX9" t="n">
-        <v>-0.02637521096477504</v>
+        <v>-0.01423899050110533</v>
       </c>
       <c r="DY9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ9" t="n">
         <v>0</v>
       </c>
       <c r="EA9" t="n">
-        <v>-0.03911918065484527</v>
+        <v>-0.1049750059353331</v>
       </c>
       <c r="EB9" t="n">
-        <v>-0.01392682863656938</v>
+        <v>0.0518270535868566</v>
       </c>
       <c r="EC9" t="n">
         <v>-0</v>
       </c>
       <c r="ED9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE9" t="n">
         <v>-0</v>
@@ -5390,76 +5390,76 @@
         <v>-0</v>
       </c>
       <c r="EG9" t="n">
-        <v>-0.003307499952264537</v>
+        <v>-0.06671262304697007</v>
       </c>
       <c r="EH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ9" t="n">
-        <v>-0.0001841213442673502</v>
+        <v>-0.05507269176084893</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.00268145251883131</v>
+        <v>0.0287640606311602</v>
       </c>
       <c r="EL9" t="n">
         <v>-0</v>
       </c>
       <c r="EM9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN9" t="n">
         <v>-0</v>
       </c>
       <c r="EO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP9" t="n">
-        <v>0.005148271772005794</v>
+        <v>-0.1237624661075212</v>
       </c>
       <c r="EQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER9" t="n">
         <v>0</v>
       </c>
       <c r="ES9" t="n">
-        <v>-0.01704112009185342</v>
+        <v>-0.2672027697682095</v>
       </c>
       <c r="ET9" t="n">
-        <v>-0.04225274952876416</v>
+        <v>-0.1978761423203395</v>
       </c>
       <c r="EU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX9" t="n">
         <v>-0</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.00165352617477248</v>
+        <v>-0.228195368576096</v>
       </c>
       <c r="EZ9" t="n">
         <v>-0</v>
       </c>
       <c r="FA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.0008961467529960714</v>
+        <v>-0.001381296677954855</v>
       </c>
       <c r="FC9" t="n">
-        <v>0.01758348386570644</v>
+        <v>0.1197112288572004</v>
       </c>
       <c r="FD9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE9" t="n">
         <v>0</v>
@@ -5471,25 +5471,25 @@
         <v>0</v>
       </c>
       <c r="FH9" t="n">
-        <v>-0.0247387304426144</v>
+        <v>-0.2018758995535767</v>
       </c>
       <c r="FI9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ9" t="n">
         <v>-0</v>
       </c>
       <c r="FK9" t="n">
-        <v>-0.03690852922928384</v>
+        <v>0.172971925587836</v>
       </c>
       <c r="FL9" t="n">
-        <v>0.002784941581781802</v>
+        <v>0.144821877601764</v>
       </c>
       <c r="FM9" t="n">
         <v>0</v>
       </c>
       <c r="FN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO9" t="n">
         <v>0</v>
@@ -5498,7 +5498,7 @@
         <v>0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>-0.00201124759772874</v>
+        <v>0.04420083096619936</v>
       </c>
       <c r="FR9" t="n">
         <v>0</v>
@@ -5507,25 +5507,25 @@
         <v>-0</v>
       </c>
       <c r="FT9" t="n">
-        <v>-0.01116101350913467</v>
+        <v>-0.06208662004495921</v>
       </c>
       <c r="FU9" t="n">
-        <v>0.02978716553309548</v>
+        <v>-0.0979670930088089</v>
       </c>
       <c r="FV9" t="n">
         <v>-0</v>
       </c>
       <c r="FW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>-0.02136075364215311</v>
+        <v>-0.1081071056248592</v>
       </c>
       <c r="GA9" t="n">
         <v>0</v>
@@ -5537,13 +5537,13 @@
         <v>-0</v>
       </c>
       <c r="GD9" t="n">
-        <v>-0.006308537710266412</v>
+        <v>0.06311477969901529</v>
       </c>
       <c r="GE9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG9" t="n">
         <v>0</v>
@@ -5554,16 +5554,16 @@
         <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>0.2734564167601566</v>
+        <v>0.3904319835668758</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.09660443159627234</v>
+        <v>-0.1950486347223729</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0895996393942753</v>
+        <v>-0.01996542301514006</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -5575,103 +5575,103 @@
         <v>-0</v>
       </c>
       <c r="I10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1621562710770767</v>
+        <v>0.3444973797254306</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.0495915838494495</v>
+        <v>-0.125444331195334</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.101446729409003</v>
+        <v>-0.07195182150987173</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P10" t="n">
         <v>-0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.06692047748750267</v>
+        <v>0.07943296168215006</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V10" t="n">
-        <v>0.01175387451106731</v>
+        <v>-0.06821575074277728</v>
       </c>
       <c r="W10" t="n">
-        <v>0.02731262264217158</v>
+        <v>-0.07527599801331898</v>
       </c>
       <c r="X10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
         <v>-0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.07791770422523368</v>
+        <v>-0.0944676658478739</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0.03415897552144039</v>
+        <v>-0.08880162232675065</v>
       </c>
       <c r="AF10" t="n">
-        <v>8.129508962701263e-05</v>
+        <v>-0.1091884117439763</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
         <v>-0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.0118989445578132</v>
+        <v>0.1495690148389067</v>
       </c>
       <c r="AM10" t="n">
         <v>-0</v>
       </c>
       <c r="AN10" t="n">
-        <v>-0.03013507178124711</v>
+        <v>-0.1040885098828721</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.07614552160684608</v>
+        <v>0.06309972096599811</v>
       </c>
       <c r="AP10" t="n">
         <v>0</v>
@@ -5680,34 +5680,34 @@
         <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS10" t="n">
         <v>0</v>
       </c>
       <c r="AT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.3569760421889527</v>
+        <v>0.3793439367487869</v>
       </c>
       <c r="AV10" t="n">
         <v>-0</v>
       </c>
       <c r="AW10" t="n">
-        <v>-0.007878739983230909</v>
+        <v>-0.1830597337630048</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.1104692799894263</v>
+        <v>-0.2660634383075624</v>
       </c>
       <c r="AY10" t="n">
         <v>-0</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB10" t="n">
         <v>-0</v>
@@ -5716,16 +5716,16 @@
         <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.02598118597127932</v>
+        <v>-0.05020229706185322</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>-0.03546209244244818</v>
+        <v>-0.02674625556588128</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.1129214120148363</v>
+        <v>-0.02045284105114521</v>
       </c>
       <c r="BH10" t="n">
         <v>0</v>
@@ -5734,7 +5734,7 @@
         <v>-0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK10" t="n">
         <v>0</v>
@@ -5743,22 +5743,22 @@
         <v>-0</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.1136075433636381</v>
+        <v>-0.02328666846503944</v>
       </c>
       <c r="BN10" t="n">
         <v>-0</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.06382652466032084</v>
+        <v>0.06157277162869901</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.08702170804305877</v>
+        <v>0.02424599020268963</v>
       </c>
       <c r="BQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS10" t="n">
         <v>-0</v>
@@ -5770,52 +5770,52 @@
         <v>-0</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.1497514782812533</v>
+        <v>0.2655519152509834</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.0004700447849649035</v>
+        <v>-0.1393775091579015</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.01680254449885207</v>
+        <v>-0.07609009095333642</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD10" t="n">
         <v>-0</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0.05263386436256628</v>
+        <v>-0.1413737547030788</v>
       </c>
       <c r="CF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.002842856773778949</v>
+        <v>0.160896141375195</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.003797638917304214</v>
+        <v>0.003742236672403941</v>
       </c>
       <c r="CI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL10" t="n">
         <v>-0</v>
@@ -5824,19 +5824,19 @@
         <v>0</v>
       </c>
       <c r="CN10" t="n">
-        <v>-0.06516722605116256</v>
+        <v>-0.08709491360633909</v>
       </c>
       <c r="CO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP10" t="n">
-        <v>-0.09379010102508724</v>
+        <v>0.2595843598325654</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-0.1053930623819967</v>
+        <v>0.1357260144145127</v>
       </c>
       <c r="CR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS10" t="n">
         <v>-0</v>
@@ -5851,49 +5851,49 @@
         <v>0</v>
       </c>
       <c r="CW10" t="n">
-        <v>-0.03246400814421799</v>
+        <v>-0.1373863586355404</v>
       </c>
       <c r="CX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.02498887779237372</v>
+        <v>0.1791177895618679</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.004411538115185219</v>
+        <v>0.01330276970795293</v>
       </c>
       <c r="DA10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE10" t="n">
         <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0.001006225835083109</v>
+        <v>-0.1285250228158621</v>
       </c>
       <c r="DG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.0203897917931117</v>
+        <v>0.07265050696571994</v>
       </c>
       <c r="DI10" t="n">
-        <v>-0.004675446090095653</v>
+        <v>-0.09619922838789599</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL10" t="n">
         <v>0</v>
@@ -5905,52 +5905,52 @@
         <v>-0</v>
       </c>
       <c r="DO10" t="n">
-        <v>-0.05240632488661994</v>
+        <v>-0.06877584610754602</v>
       </c>
       <c r="DP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>-0.05954957727568773</v>
+        <v>0.06237767287420341</v>
       </c>
       <c r="DR10" t="n">
-        <v>-0.005942701853838405</v>
+        <v>-0.03615584454566256</v>
       </c>
       <c r="DS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.04619829760963263</v>
+        <v>0.04574114141764936</v>
       </c>
       <c r="DY10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ10" t="n">
-        <v>-0.03741375074824214</v>
+        <v>0.0435365015890797</v>
       </c>
       <c r="EA10" t="n">
-        <v>-0.01348688789214232</v>
+        <v>-0.002215071517147445</v>
       </c>
       <c r="EB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE10" t="n">
         <v>-0</v>
@@ -5959,100 +5959,100 @@
         <v>0</v>
       </c>
       <c r="EG10" t="n">
-        <v>-0.02030781187226492</v>
+        <v>-0.09144917109130046</v>
       </c>
       <c r="EH10" t="n">
         <v>-0</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.06986252407970357</v>
+        <v>0.1424197784085807</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.04982624885588373</v>
+        <v>0.02157917904774224</v>
       </c>
       <c r="EK10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN10" t="n">
         <v>-0</v>
       </c>
       <c r="EO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP10" t="n">
-        <v>-0.04279462823148703</v>
+        <v>-0.07184898557034179</v>
       </c>
       <c r="EQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER10" t="n">
-        <v>-0.04553868717649914</v>
+        <v>-0.1223582017532911</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.00419535455121062</v>
+        <v>-0.01847647118954035</v>
       </c>
       <c r="ET10" t="n">
         <v>-0</v>
       </c>
       <c r="EU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV10" t="n">
         <v>0</v>
       </c>
       <c r="EW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY10" t="n">
-        <v>-0.04094949638805737</v>
+        <v>-0.1545983133866907</v>
       </c>
       <c r="EZ10" t="n">
         <v>-0</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.0178671006777913</v>
+        <v>0.1850343198073415</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.01658768417924171</v>
+        <v>-0.004193771782156277</v>
       </c>
       <c r="FC10" t="n">
         <v>-0</v>
       </c>
       <c r="FD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG10" t="n">
         <v>0</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.05632367523219518</v>
+        <v>-0.09855050853172151</v>
       </c>
       <c r="FI10" t="n">
         <v>-0</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.05326418999692722</v>
+        <v>0.112778891613021</v>
       </c>
       <c r="FK10" t="n">
-        <v>-0.0119192198258514</v>
+        <v>-0.01771138254518826</v>
       </c>
       <c r="FL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM10" t="n">
         <v>0</v>
@@ -6061,22 +6061,22 @@
         <v>-0</v>
       </c>
       <c r="FO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>-0.01000505309144677</v>
+        <v>0.0120869271293769</v>
       </c>
       <c r="FR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS10" t="n">
-        <v>0.01047431542355796</v>
+        <v>0.170472089242109</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.04751249312881812</v>
+        <v>-0.03273818816825298</v>
       </c>
       <c r="FU10" t="n">
         <v>0</v>
@@ -6091,28 +6091,28 @@
         <v>0</v>
       </c>
       <c r="FY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>-0.003868034690075963</v>
+        <v>-0.1140009711531688</v>
       </c>
       <c r="GA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB10" t="n">
-        <v>-0.01324834418027273</v>
+        <v>0.09834779818047407</v>
       </c>
       <c r="GC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE10" t="n">
         <v>-0</v>
       </c>
       <c r="GF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG10" t="n">
         <v>0</v>
@@ -6692,43 +6692,43 @@
         <v>-0</v>
       </c>
       <c r="B12" t="n">
-        <v>0.2624116359387804</v>
+        <v>0.134382179171905</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.03881939443125872</v>
+        <v>-0.03569829649356943</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.05930305353265004</v>
+        <v>-0.04558743588138756</v>
       </c>
       <c r="F12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>-0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1366569601774322</v>
+        <v>0.1247312314481834</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.01493843849999751</v>
+        <v>-0.02010445045873602</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.05418528308489518</v>
+        <v>-0.05830871375463341</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -6737,28 +6737,28 @@
         <v>-0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.04493308492445113</v>
+        <v>0.02824303382018484</v>
       </c>
       <c r="U12" t="n">
         <v>-0</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.01316339545839634</v>
+        <v>-0.003994652412343105</v>
       </c>
       <c r="W12" t="n">
-        <v>0.03743774499274665</v>
+        <v>0.001098458773500672</v>
       </c>
       <c r="X12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
         <v>-0</v>
@@ -6767,49 +6767,49 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.07218816005789898</v>
+        <v>-0.01686626402719555</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0.02118107628822657</v>
+        <v>-0.06662565086737694</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.001351879340714758</v>
+        <v>-0.07569388703149797</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>-0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL12" t="n">
-        <v>-0.01593818829408705</v>
+        <v>0.04846585235150418</v>
       </c>
       <c r="AM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>-0.01626551253329821</v>
+        <v>-0.005760651850945736</v>
       </c>
       <c r="AO12" t="n">
-        <v>-0.04857449964241929</v>
+        <v>0.04372928662773706</v>
       </c>
       <c r="AP12" t="n">
         <v>0</v>
@@ -6818,34 +6818,34 @@
         <v>-0</v>
       </c>
       <c r="AR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS12" t="n">
         <v>-0</v>
       </c>
       <c r="AT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.2755598222233201</v>
+        <v>0.1516933377064243</v>
       </c>
       <c r="AV12" t="n">
         <v>-0</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.03253363828655369</v>
+        <v>-0.003214478550336535</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.06078775272059511</v>
+        <v>-0.08750622974888166</v>
       </c>
       <c r="AY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
         <v>-0</v>
@@ -6854,25 +6854,25 @@
         <v>-0</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.02748416402455224</v>
+        <v>-0.03731825153938752</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>-0.06103839168169392</v>
+        <v>-0.01659677633898527</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.06593262662332867</v>
+        <v>-0.01496529461097597</v>
       </c>
       <c r="BH12" t="n">
         <v>0</v>
       </c>
       <c r="BI12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK12" t="n">
         <v>0</v>
@@ -6881,19 +6881,19 @@
         <v>-0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.1044795212856029</v>
+        <v>0.03090424246294251</v>
       </c>
       <c r="BN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.02370464895777139</v>
+        <v>0.02068577131570232</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.09933668161081831</v>
+        <v>0.06227500259351626</v>
       </c>
       <c r="BQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR12" t="n">
         <v>0</v>
@@ -6905,28 +6905,28 @@
         <v>-0</v>
       </c>
       <c r="BU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.1256849148602937</v>
+        <v>0.1091824405210198</v>
       </c>
       <c r="BW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.02373396834097652</v>
+        <v>-0.02605641912325125</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.02657224830090911</v>
+        <v>-0.009060796287256192</v>
       </c>
       <c r="BZ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA12" t="n">
         <v>-0</v>
       </c>
       <c r="CB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC12" t="n">
         <v>-0</v>
@@ -6935,16 +6935,16 @@
         <v>-0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.05149450331862825</v>
+        <v>-0.04203855176409858</v>
       </c>
       <c r="CF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG12" t="n">
-        <v>-0.005129242792431028</v>
+        <v>0.03532638941590903</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.005766829502282254</v>
+        <v>0.0230028818003898</v>
       </c>
       <c r="CI12" t="n">
         <v>-0</v>
@@ -6956,49 +6956,49 @@
         <v>0</v>
       </c>
       <c r="CL12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM12" t="n">
         <v>0</v>
       </c>
       <c r="CN12" t="n">
-        <v>-0.0518822534491421</v>
+        <v>-0.05613518964657489</v>
       </c>
       <c r="CO12" t="n">
         <v>-0</v>
       </c>
       <c r="CP12" t="n">
-        <v>-0.05073182828579114</v>
+        <v>0.04353726277758535</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-0.06716966590625414</v>
+        <v>0.02944404061497065</v>
       </c>
       <c r="CR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.03058512312720336</v>
+        <v>-0.03943700270267848</v>
       </c>
       <c r="CX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.009337990881361198</v>
+        <v>0.03934992722802814</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.0009719031305633427</v>
+        <v>0.02655245131009553</v>
       </c>
       <c r="DA12" t="n">
         <v>0</v>
@@ -7016,73 +7016,73 @@
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>-0.008662007772379189</v>
+        <v>-0.0004469848841822218</v>
       </c>
       <c r="DG12" t="n">
         <v>0</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.05361434618927224</v>
+        <v>0.00835047530936823</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.007362391663991064</v>
+        <v>-0.006612302869312424</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL12" t="n">
         <v>0</v>
       </c>
       <c r="DM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN12" t="n">
         <v>-0</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.05501325367481425</v>
+        <v>-0.03998808710426163</v>
       </c>
       <c r="DP12" t="n">
         <v>0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.007369380160160022</v>
+        <v>-0.02467818281101245</v>
       </c>
       <c r="DR12" t="n">
-        <v>-0.01560492187590726</v>
+        <v>-0.01813886689114099</v>
       </c>
       <c r="DS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU12" t="n">
         <v>-0</v>
       </c>
       <c r="DV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW12" t="n">
         <v>-0</v>
       </c>
       <c r="DX12" t="n">
-        <v>-0.00247315305874347</v>
+        <v>0.0430960968624499</v>
       </c>
       <c r="DY12" t="n">
         <v>0</v>
       </c>
       <c r="DZ12" t="n">
-        <v>-0.006236684246898113</v>
+        <v>0.02029458698328013</v>
       </c>
       <c r="EA12" t="n">
-        <v>-0.01706178636936942</v>
+        <v>-0.05570181813331887</v>
       </c>
       <c r="EB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC12" t="n">
         <v>0</v>
@@ -7091,22 +7091,22 @@
         <v>0</v>
       </c>
       <c r="EE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.02545061933391383</v>
+        <v>0.008372806444731857</v>
       </c>
       <c r="EH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.001417048226673886</v>
+        <v>0.0274469752366307</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.06124057598746319</v>
+        <v>0.04631746226418131</v>
       </c>
       <c r="EK12" t="n">
         <v>-0</v>
@@ -7115,7 +7115,7 @@
         <v>-0</v>
       </c>
       <c r="EM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN12" t="n">
         <v>-0</v>
@@ -7124,25 +7124,25 @@
         <v>0</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.02828110190642648</v>
+        <v>-0.03291840423867026</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.008571980021333508</v>
+        <v>0.04348582888960041</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.02350927181110672</v>
+        <v>-0.003000522772718701</v>
       </c>
       <c r="ET12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW12" t="n">
         <v>-0</v>
@@ -7151,16 +7151,16 @@
         <v>-0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.03018744284991489</v>
+        <v>-0.04728312377916968</v>
       </c>
       <c r="EZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.002365772596215269</v>
+        <v>0.04729563611662369</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.01313878347749324</v>
+        <v>0.01458736294118737</v>
       </c>
       <c r="FC12" t="n">
         <v>-0</v>
@@ -7175,46 +7175,46 @@
         <v>-0</v>
       </c>
       <c r="FG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.01819826711347194</v>
+        <v>-0.0007769616327067139</v>
       </c>
       <c r="FI12" t="n">
         <v>-0</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.016857340948536</v>
+        <v>-0.008373562147262514</v>
       </c>
       <c r="FK12" t="n">
-        <v>-0.03005815009609287</v>
+        <v>-0.02005107398578592</v>
       </c>
       <c r="FL12" t="n">
         <v>-0</v>
       </c>
       <c r="FM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>-0.03820954570002701</v>
+        <v>0.01791357078661364</v>
       </c>
       <c r="FR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS12" t="n">
-        <v>-0.02249132432566002</v>
+        <v>0.04280450888320717</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.00853985112703123</v>
+        <v>-0.05246144826150572</v>
       </c>
       <c r="FU12" t="n">
         <v>0</v>
@@ -7223,7 +7223,7 @@
         <v>0</v>
       </c>
       <c r="FW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX12" t="n">
         <v>0</v>
@@ -7232,19 +7232,19 @@
         <v>-0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>0.01094890968190659</v>
+        <v>-0.01834572334622289</v>
       </c>
       <c r="GA12" t="n">
         <v>-0</v>
       </c>
       <c r="GB12" t="n">
-        <v>-0.02886883367954961</v>
+        <v>-0.0004507774446928631</v>
       </c>
       <c r="GC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE12" t="n">
         <v>-0</v>
@@ -7253,7 +7253,7 @@
         <v>0</v>
       </c>
       <c r="GG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -7261,19 +7261,19 @@
         <v>0</v>
       </c>
       <c r="B13" t="n">
-        <v>0.2073893506791554</v>
+        <v>0.2211835323703555</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.004609413240204317</v>
+        <v>-0.06267163628245191</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1357087275226383</v>
+        <v>-0.1650354934627269</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -7285,76 +7285,76 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1379925636361579</v>
+        <v>0.431763805028794</v>
       </c>
       <c r="L13" t="n">
         <v>-0</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.01555814265892296</v>
+        <v>-0.1338198258174661</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.1004248224496198</v>
+        <v>-0.1537107474726792</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>-0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.01245442944959972</v>
+        <v>0.08107458135832543</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.009546788573206164</v>
+        <v>-0.08963089919326224</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.002454340294905252</v>
+        <v>-0.01093483816955005</v>
       </c>
       <c r="Y13" t="n">
         <v>-0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB13" t="n">
         <v>-0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.02964924391349954</v>
+        <v>-0.03268444187051701</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.01918874406522028</v>
+        <v>-0.2886107820181839</v>
       </c>
       <c r="AG13" t="n">
-        <v>-0.01123911717718969</v>
+        <v>-0.05117409771006064</v>
       </c>
       <c r="AH13" t="n">
         <v>-0</v>
@@ -7363,67 +7363,67 @@
         <v>-0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.006903154029141725</v>
+        <v>0.04476505031078178</v>
       </c>
       <c r="AM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
         <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>-0.01681150772418931</v>
+        <v>-0.02334793066657892</v>
       </c>
       <c r="AP13" t="n">
-        <v>-0.03485312776978189</v>
+        <v>-0.03311103992949142</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS13" t="n">
         <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.1512650474430794</v>
+        <v>0.5348056869034494</v>
       </c>
       <c r="AV13" t="n">
         <v>-0</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX13" t="n">
-        <v>-0.001119795215973237</v>
+        <v>-0.1725785872444521</v>
       </c>
       <c r="AY13" t="n">
-        <v>-0.06953944299165316</v>
+        <v>-0.1289198434045886</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
         <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.06879364902693798</v>
+        <v>-0.1147119020245292</v>
       </c>
       <c r="BE13" t="n">
         <v>0</v>
@@ -7432,25 +7432,25 @@
         <v>0</v>
       </c>
       <c r="BG13" t="n">
-        <v>-0.03646778644263521</v>
+        <v>-0.1236926352376043</v>
       </c>
       <c r="BH13" t="n">
-        <v>-0.06030724000733129</v>
+        <v>-0.05010261429482203</v>
       </c>
       <c r="BI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.06474366697097311</v>
+        <v>0.1788021080655961</v>
       </c>
       <c r="BN13" t="n">
         <v>0</v>
@@ -7459,16 +7459,16 @@
         <v>-0</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.04197359140605972</v>
+        <v>0.09516873476247885</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.008312104286500923</v>
+        <v>0.002456717620562007</v>
       </c>
       <c r="BR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT13" t="n">
         <v>0</v>
@@ -7477,19 +7477,19 @@
         <v>-0</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.060488453200599</v>
+        <v>0.296878812876552</v>
       </c>
       <c r="BW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX13" t="n">
         <v>0</v>
       </c>
       <c r="BY13" t="n">
-        <v>-0.008511551806860132</v>
+        <v>-0.0640848335852274</v>
       </c>
       <c r="BZ13" t="n">
-        <v>-0.01226632062692334</v>
+        <v>-0.03973652679038923</v>
       </c>
       <c r="CA13" t="n">
         <v>-0</v>
@@ -7498,67 +7498,67 @@
         <v>0</v>
       </c>
       <c r="CC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD13" t="n">
         <v>-0</v>
       </c>
       <c r="CE13" t="n">
-        <v>-0.03875181760277759</v>
+        <v>-0.07617771696984563</v>
       </c>
       <c r="CF13" t="n">
         <v>0</v>
       </c>
       <c r="CG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH13" t="n">
-        <v>-0.005541690231554492</v>
+        <v>0.05641583375550662</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.03011665716240493</v>
+        <v>0.07127663661177482</v>
       </c>
       <c r="CJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK13" t="n">
         <v>0</v>
       </c>
       <c r="CL13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM13" t="n">
         <v>0</v>
       </c>
       <c r="CN13" t="n">
-        <v>-0.02620838741303694</v>
+        <v>-0.2917415369124596</v>
       </c>
       <c r="CO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.01756152726957533</v>
+        <v>0.1856425612513307</v>
       </c>
       <c r="CR13" t="n">
-        <v>-0.01517050654401123</v>
+        <v>0.0836563017357035</v>
       </c>
       <c r="CS13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT13" t="n">
         <v>-0</v>
       </c>
       <c r="CU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV13" t="n">
         <v>0</v>
       </c>
       <c r="CW13" t="n">
-        <v>-0.02540792953485304</v>
+        <v>-0.06538991113006618</v>
       </c>
       <c r="CX13" t="n">
         <v>-0</v>
@@ -7567,10 +7567,10 @@
         <v>0</v>
       </c>
       <c r="CZ13" t="n">
-        <v>-0.005543716105433154</v>
+        <v>0.02499359722950545</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.0280374567710711</v>
+        <v>0.07843543075733465</v>
       </c>
       <c r="DB13" t="n">
         <v>0</v>
@@ -7582,28 +7582,28 @@
         <v>0</v>
       </c>
       <c r="DE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF13" t="n">
-        <v>-0.01202693933698795</v>
+        <v>0.01837083052263476</v>
       </c>
       <c r="DG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.00243900778609646</v>
+        <v>-0.04055885448939141</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.004398172868571877</v>
+        <v>-0.001309613316910752</v>
       </c>
       <c r="DK13" t="n">
         <v>0</v>
       </c>
       <c r="DL13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM13" t="n">
         <v>0</v>
@@ -7612,88 +7612,88 @@
         <v>-0</v>
       </c>
       <c r="DO13" t="n">
-        <v>-0.02710477535702198</v>
+        <v>-0.1156557880786263</v>
       </c>
       <c r="DP13" t="n">
         <v>0</v>
       </c>
       <c r="DQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.01002641131483205</v>
+        <v>0.09391387501555623</v>
       </c>
       <c r="DS13" t="n">
-        <v>-0.009003828289221954</v>
+        <v>0.004549609549797478</v>
       </c>
       <c r="DT13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU13" t="n">
         <v>-0</v>
       </c>
       <c r="DV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW13" t="n">
         <v>-0</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.001541149974254064</v>
+        <v>0.05558720089499688</v>
       </c>
       <c r="DY13" t="n">
         <v>0</v>
       </c>
       <c r="DZ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA13" t="n">
-        <v>-0.01375630952216829</v>
+        <v>-0.01773205321624393</v>
       </c>
       <c r="EB13" t="n">
-        <v>-0.009617710227955123</v>
+        <v>-0.07990465228408264</v>
       </c>
       <c r="EC13" t="n">
         <v>-0</v>
       </c>
       <c r="ED13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF13" t="n">
         <v>-0</v>
       </c>
       <c r="EG13" t="n">
-        <v>-0.01657366460068689</v>
+        <v>0.06430418525819777</v>
       </c>
       <c r="EH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI13" t="n">
         <v>0</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.006847755167527577</v>
+        <v>-0.01065817228107018</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.01975202521851369</v>
+        <v>0.04080869878877032</v>
       </c>
       <c r="EL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM13" t="n">
         <v>-0</v>
       </c>
       <c r="EN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP13" t="n">
-        <v>-0.01952679253474292</v>
+        <v>0.0158275436312587</v>
       </c>
       <c r="EQ13" t="n">
         <v>0</v>
@@ -7702,25 +7702,25 @@
         <v>-0</v>
       </c>
       <c r="ES13" t="n">
-        <v>-0.0006303549022507892</v>
+        <v>-0.05288702090353849</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.04278030465385839</v>
+        <v>0.06334898266905202</v>
       </c>
       <c r="EU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV13" t="n">
         <v>0</v>
       </c>
       <c r="EW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX13" t="n">
         <v>-0</v>
       </c>
       <c r="EY13" t="n">
-        <v>-0.02818642620242703</v>
+        <v>-0.08484367222447882</v>
       </c>
       <c r="EZ13" t="n">
         <v>0</v>
@@ -7729,25 +7729,25 @@
         <v>-0</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.0003964469772894106</v>
+        <v>0.01997593633089768</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.03253667398185735</v>
+        <v>0.07289319526263022</v>
       </c>
       <c r="FD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE13" t="n">
         <v>0</v>
       </c>
       <c r="FF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG13" t="n">
         <v>0</v>
       </c>
       <c r="FH13" t="n">
-        <v>-0.00505966031444571</v>
+        <v>-0.05871326975172775</v>
       </c>
       <c r="FI13" t="n">
         <v>-0</v>
@@ -7756,52 +7756,52 @@
         <v>-0</v>
       </c>
       <c r="FK13" t="n">
-        <v>-0.02207738252416749</v>
+        <v>0.03821935681591922</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.01714012440061239</v>
+        <v>0.04486619129107695</v>
       </c>
       <c r="FM13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>-0.01410608376747276</v>
+        <v>-0.02968021855095043</v>
       </c>
       <c r="FR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FT13" t="n">
-        <v>-0.02739021916414078</v>
+        <v>-0.09473502296807192</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.001314136345316307</v>
+        <v>0.006281626859084835</v>
       </c>
       <c r="FV13" t="n">
         <v>-0</v>
       </c>
       <c r="FW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY13" t="n">
         <v>-0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>-0.02778717149166223</v>
+        <v>0.01627048267473629</v>
       </c>
       <c r="GA13" t="n">
         <v>-0</v>
@@ -7813,7 +7813,7 @@
         <v>0</v>
       </c>
       <c r="GD13" t="n">
-        <v>-0.02222435366379504</v>
+        <v>-0.0262203941242582</v>
       </c>
       <c r="GE13" t="n">
         <v>-0</v>
@@ -7827,28 +7827,28 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B14" t="n">
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>0.342970196518474</v>
+        <v>0.2031663683772587</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.1097515327279935</v>
+        <v>-0.1407117156347355</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.07141131794219462</v>
+        <v>0.1427643468092199</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -7857,25 +7857,25 @@
         <v>-0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2738566767456348</v>
+        <v>0.2021514205452867</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.1278609334685742</v>
+        <v>-0.165349930261914</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.1402247354580816</v>
+        <v>0.06696808446069892</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -7887,19 +7887,19 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0898069982008298</v>
+        <v>0.03452980051202631</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.02219012329727756</v>
+        <v>-0.03994095573007739</v>
       </c>
       <c r="W14" t="n">
-        <v>0.03283356269470165</v>
+        <v>-0.04669255266767385</v>
       </c>
       <c r="X14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
         <v>-0</v>
@@ -7911,79 +7911,79 @@
         <v>-0</v>
       </c>
       <c r="AC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.06426784352370626</v>
+        <v>0.04553124553373938</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.04699573585661168</v>
+        <v>0.1024646800297219</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.02461271060332367</v>
+        <v>0.04310566225303637</v>
       </c>
       <c r="AG14" t="n">
         <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>-0.02307886884534528</v>
+        <v>0.05406391132964766</v>
       </c>
       <c r="AN14" t="n">
-        <v>-0.03288830313013368</v>
+        <v>-0.05852119155206835</v>
       </c>
       <c r="AO14" t="n">
-        <v>-0.08425828309962584</v>
+        <v>0.0004626230667029018</v>
       </c>
       <c r="AP14" t="n">
         <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.1595743929262506</v>
+        <v>0.1993320463010466</v>
       </c>
       <c r="AW14" t="n">
-        <v>-0.02322273317365001</v>
+        <v>-0.2268786571062467</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.1652389883018708</v>
+        <v>-0.01970227586730812</v>
       </c>
       <c r="AY14" t="n">
         <v>-0</v>
       </c>
       <c r="AZ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB14" t="n">
         <v>-0</v>
@@ -7992,16 +7992,16 @@
         <v>-0</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.09872972827781143</v>
+        <v>-0.01238684023363018</v>
       </c>
       <c r="BF14" t="n">
-        <v>-0.04669224878704851</v>
+        <v>0.1340527273350162</v>
       </c>
       <c r="BG14" t="n">
-        <v>-0.08757230315296104</v>
+        <v>0.08115311813682992</v>
       </c>
       <c r="BH14" t="n">
         <v>0</v>
@@ -8016,49 +8016,49 @@
         <v>0</v>
       </c>
       <c r="BL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BN14" t="n">
-        <v>0.03983958074702239</v>
+        <v>-0.06030135854029023</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.05920005311724343</v>
+        <v>-0.08066455695969676</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.129933395322922</v>
+        <v>-0.1292020979343453</v>
       </c>
       <c r="BQ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS14" t="n">
         <v>0</v>
       </c>
       <c r="BT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BW14" t="n">
-        <v>0.05314719140800196</v>
+        <v>0.09721625055393802</v>
       </c>
       <c r="BX14" t="n">
-        <v>-0.01467073408744076</v>
+        <v>-0.0803368288880927</v>
       </c>
       <c r="BY14" t="n">
-        <v>0.09636595815116242</v>
+        <v>-0.02546479956150703</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA14" t="n">
         <v>0</v>
@@ -8067,28 +8067,28 @@
         <v>-0</v>
       </c>
       <c r="CC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE14" t="n">
         <v>0</v>
       </c>
       <c r="CF14" t="n">
-        <v>-0.07198410961931657</v>
+        <v>-0.07861226057690586</v>
       </c>
       <c r="CG14" t="n">
-        <v>0.02509372377254469</v>
+        <v>0.07268067817461352</v>
       </c>
       <c r="CH14" t="n">
-        <v>0.002765312141491885</v>
+        <v>-0.03105972465713358</v>
       </c>
       <c r="CI14" t="n">
         <v>0</v>
       </c>
       <c r="CJ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK14" t="n">
         <v>0</v>
@@ -8097,19 +8097,19 @@
         <v>-0</v>
       </c>
       <c r="CM14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CO14" t="n">
-        <v>0.0157259551637416</v>
+        <v>-0.0152213403069345</v>
       </c>
       <c r="CP14" t="n">
-        <v>-0.007232599217462946</v>
+        <v>0.17202042509536</v>
       </c>
       <c r="CQ14" t="n">
-        <v>-0.134030388334011</v>
+        <v>0.01983684806665717</v>
       </c>
       <c r="CR14" t="n">
         <v>0</v>
@@ -8118,34 +8118,34 @@
         <v>0</v>
       </c>
       <c r="CT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU14" t="n">
         <v>-0</v>
       </c>
       <c r="CV14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CX14" t="n">
-        <v>-0.05447512606266257</v>
+        <v>-0.05784014068397651</v>
       </c>
       <c r="CY14" t="n">
-        <v>0.02501838199046121</v>
+        <v>0.07015821153237836</v>
       </c>
       <c r="CZ14" t="n">
-        <v>0.02713359366719531</v>
+        <v>-0.04650525817935287</v>
       </c>
       <c r="DA14" t="n">
         <v>-0</v>
       </c>
       <c r="DB14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD14" t="n">
         <v>0</v>
@@ -8154,16 +8154,16 @@
         <v>-0</v>
       </c>
       <c r="DF14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DG14" t="n">
-        <v>-0.03707849523066748</v>
+        <v>-0.01125498461567062</v>
       </c>
       <c r="DH14" t="n">
-        <v>0.04550360450758483</v>
+        <v>0.02739623101615173</v>
       </c>
       <c r="DI14" t="n">
-        <v>-0.00680358613817661</v>
+        <v>-0.02331957611138215</v>
       </c>
       <c r="DJ14" t="n">
         <v>0</v>
@@ -8175,31 +8175,31 @@
         <v>0</v>
       </c>
       <c r="DM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO14" t="n">
         <v>-0</v>
       </c>
       <c r="DP14" t="n">
-        <v>-0.003156122121830755</v>
+        <v>-0.02302751005764581</v>
       </c>
       <c r="DQ14" t="n">
-        <v>0.02956404662718841</v>
+        <v>0.06371845925258245</v>
       </c>
       <c r="DR14" t="n">
-        <v>-0.1504434517564663</v>
+        <v>-0.06197546923819081</v>
       </c>
       <c r="DS14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT14" t="n">
         <v>-0</v>
       </c>
       <c r="DU14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV14" t="n">
         <v>0</v>
@@ -8208,16 +8208,16 @@
         <v>-0</v>
       </c>
       <c r="DX14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DY14" t="n">
-        <v>0.06134807659331291</v>
+        <v>0.02436552677783661</v>
       </c>
       <c r="DZ14" t="n">
-        <v>0.003502486305162758</v>
+        <v>0.02514121832756418</v>
       </c>
       <c r="EA14" t="n">
-        <v>-0.06389529179402857</v>
+        <v>0.04441827750162265</v>
       </c>
       <c r="EB14" t="n">
         <v>0</v>
@@ -8232,46 +8232,46 @@
         <v>-0</v>
       </c>
       <c r="EF14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EH14" t="n">
-        <v>-0.1143604660715261</v>
+        <v>-0.03995863905222927</v>
       </c>
       <c r="EI14" t="n">
-        <v>0.05244576720599337</v>
+        <v>0.04788642181336052</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.06638098822878905</v>
+        <v>0.01786017429252081</v>
       </c>
       <c r="EK14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN14" t="n">
         <v>-0</v>
       </c>
       <c r="EO14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP14" t="n">
         <v>0</v>
       </c>
       <c r="EQ14" t="n">
-        <v>-0.007602853461317472</v>
+        <v>-0.04669092531631137</v>
       </c>
       <c r="ER14" t="n">
-        <v>0.03277591048267625</v>
+        <v>0.07629484031189114</v>
       </c>
       <c r="ES14" t="n">
-        <v>0.02644310966726408</v>
+        <v>0.01524621880531175</v>
       </c>
       <c r="ET14" t="n">
         <v>0</v>
@@ -8280,79 +8280,79 @@
         <v>0</v>
       </c>
       <c r="EV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EZ14" t="n">
-        <v>-0.06821644659536467</v>
+        <v>-0.06468576665128063</v>
       </c>
       <c r="FA14" t="n">
-        <v>0.04100492745836462</v>
+        <v>0.1084687177008568</v>
       </c>
       <c r="FB14" t="n">
-        <v>0.02452896192668477</v>
+        <v>-0.03010400741768713</v>
       </c>
       <c r="FC14" t="n">
         <v>0</v>
       </c>
       <c r="FD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG14" t="n">
         <v>0</v>
       </c>
       <c r="FH14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FI14" t="n">
-        <v>-0.005158136240674969</v>
+        <v>-0.01754975497858886</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.0011531778052613</v>
+        <v>0.06082317921820336</v>
       </c>
       <c r="FK14" t="n">
-        <v>0.07860345749122406</v>
+        <v>-0.03365918797016241</v>
       </c>
       <c r="FL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM14" t="n">
         <v>0</v>
       </c>
       <c r="FN14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO14" t="n">
         <v>-0</v>
       </c>
       <c r="FP14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FR14" t="n">
-        <v>-0.004244804252954616</v>
+        <v>-0.0003744790256449767</v>
       </c>
       <c r="FS14" t="n">
-        <v>-0.007227238551969782</v>
+        <v>-0.00771373471782752</v>
       </c>
       <c r="FT14" t="n">
-        <v>0.0967967429214432</v>
+        <v>0.2238947733548228</v>
       </c>
       <c r="FU14" t="n">
         <v>0</v>
@@ -8361,22 +8361,22 @@
         <v>-0</v>
       </c>
       <c r="FW14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GA14" t="n">
-        <v>0.05079393359683145</v>
+        <v>-0.02559187322135254</v>
       </c>
       <c r="GB14" t="n">
-        <v>-0.04844318096004517</v>
+        <v>0.1451283228112003</v>
       </c>
       <c r="GC14" t="n">
         <v>-0</v>
@@ -8399,22 +8399,22 @@
         <v>-0</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.2522417388984197</v>
+        <v>-0.270882898152466</v>
       </c>
       <c r="C15" t="n">
         <v>-0</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.3555819454258746</v>
+        <v>0.07461694997335368</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9376872490640334</v>
+        <v>0.3525372615466967</v>
       </c>
       <c r="G15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -8426,7 +8426,7 @@
         <v>-0</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.2279330814242219</v>
+        <v>-0.2419904023244663</v>
       </c>
       <c r="L15" t="n">
         <v>-0</v>
@@ -8435,10 +8435,10 @@
         <v>-0</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3489775222388402</v>
+        <v>0.1938172923776949</v>
       </c>
       <c r="O15" t="n">
-        <v>0.7527365532307281</v>
+        <v>0.2880074576129809</v>
       </c>
       <c r="P15" t="n">
         <v>-0</v>
@@ -8453,22 +8453,22 @@
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0.03505482237846016</v>
+        <v>-0.06190689960976468</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V15" t="n">
         <v>-0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.0178964885517884</v>
+        <v>0.08549280529238326</v>
       </c>
       <c r="X15" t="n">
-        <v>0.1032566813602111</v>
+        <v>0.01749222389627856</v>
       </c>
       <c r="Y15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
@@ -8477,22 +8477,22 @@
         <v>-0</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC15" t="n">
-        <v>-0.07120656509002858</v>
+        <v>-0.01307991790369076</v>
       </c>
       <c r="AD15" t="n">
         <v>-0</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF15" t="n">
-        <v>-0.1191441618537049</v>
+        <v>0.1541168642701767</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.0709193104892494</v>
+        <v>0.06038467064809384</v>
       </c>
       <c r="AH15" t="n">
         <v>-0</v>
@@ -8501,28 +8501,28 @@
         <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK15" t="n">
         <v>-0</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.01210109388651744</v>
+        <v>-0.1317177483088792</v>
       </c>
       <c r="AM15" t="n">
         <v>-0</v>
       </c>
       <c r="AN15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO15" t="n">
-        <v>-0.08212798343526145</v>
+        <v>-0.04688278852133085</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.1339004182639238</v>
+        <v>0.09942443406658895</v>
       </c>
       <c r="AQ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR15" t="n">
         <v>0</v>
@@ -8531,49 +8531,49 @@
         <v>-0</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU15" t="n">
-        <v>-0.06864689510343366</v>
+        <v>-0.3036942599761991</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX15" t="n">
-        <v>-0.04417087284402579</v>
+        <v>0.1252405898491979</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.4277892449536332</v>
+        <v>0.1616522314045085</v>
       </c>
       <c r="AZ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA15" t="n">
         <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC15" t="n">
         <v>-0</v>
       </c>
       <c r="BD15" t="n">
-        <v>-0.2053232061645263</v>
+        <v>0.01714890849535421</v>
       </c>
       <c r="BE15" t="n">
         <v>-0</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG15" t="n">
-        <v>-0.04354118282295492</v>
+        <v>0.1506533424839442</v>
       </c>
       <c r="BH15" t="n">
-        <v>0.2797344161551931</v>
+        <v>0.1020022327378811</v>
       </c>
       <c r="BI15" t="n">
         <v>-0</v>
@@ -8582,13 +8582,13 @@
         <v>0</v>
       </c>
       <c r="BK15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL15" t="n">
         <v>-0</v>
       </c>
       <c r="BM15" t="n">
-        <v>-0.05731961359152688</v>
+        <v>-0.01398245762864202</v>
       </c>
       <c r="BN15" t="n">
         <v>0</v>
@@ -8597,13 +8597,13 @@
         <v>0</v>
       </c>
       <c r="BP15" t="n">
-        <v>-0.03449166945187442</v>
+        <v>-0.08543052872108543</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0.06793768519851884</v>
+        <v>-0.02230104661223105</v>
       </c>
       <c r="BR15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS15" t="n">
         <v>-0</v>
@@ -8615,49 +8615,49 @@
         <v>-0</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.005841159922310395</v>
+        <v>-0.1586699409291602</v>
       </c>
       <c r="BW15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY15" t="n">
-        <v>-0.04587473894242786</v>
+        <v>0.06576513730360833</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0.3034794440231323</v>
+        <v>0.1121120581584971</v>
       </c>
       <c r="CA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB15" t="n">
         <v>0</v>
       </c>
       <c r="CC15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD15" t="n">
         <v>0</v>
       </c>
       <c r="CE15" t="n">
-        <v>0.06631759443131352</v>
+        <v>0.1011603792080142</v>
       </c>
       <c r="CF15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH15" t="n">
-        <v>0.08057278404511396</v>
+        <v>-0.02867036237865437</v>
       </c>
       <c r="CI15" t="n">
-        <v>-0.1225298537445581</v>
+        <v>-0.08375231509063019</v>
       </c>
       <c r="CJ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK15" t="n">
         <v>-0</v>
@@ -8666,28 +8666,28 @@
         <v>-0</v>
       </c>
       <c r="CM15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN15" t="n">
-        <v>0.05381396217216972</v>
+        <v>0.1511803222070015</v>
       </c>
       <c r="CO15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CQ15" t="n">
-        <v>-0.2256315891771361</v>
+        <v>-0.1976820028391769</v>
       </c>
       <c r="CR15" t="n">
-        <v>0.08054893000587018</v>
+        <v>-0.06559527392541444</v>
       </c>
       <c r="CS15" t="n">
         <v>-0</v>
       </c>
       <c r="CT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU15" t="n">
         <v>0</v>
@@ -8696,19 +8696,19 @@
         <v>0</v>
       </c>
       <c r="CW15" t="n">
-        <v>0.06840986987285604</v>
+        <v>0.08291283108821924</v>
       </c>
       <c r="CX15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ15" t="n">
-        <v>0.04745818842894682</v>
+        <v>-0.03514191763504477</v>
       </c>
       <c r="DA15" t="n">
-        <v>-0.1177911192601196</v>
+        <v>-0.09720693603703276</v>
       </c>
       <c r="DB15" t="n">
         <v>-0</v>
@@ -8717,52 +8717,52 @@
         <v>0</v>
       </c>
       <c r="DD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE15" t="n">
         <v>-0</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.03908834128512888</v>
+        <v>0.03506801422031398</v>
       </c>
       <c r="DG15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI15" t="n">
-        <v>-0.02965071864288949</v>
+        <v>0.02172127500142701</v>
       </c>
       <c r="DJ15" t="n">
-        <v>-0.01350700871079513</v>
+        <v>-0.03995334123817956</v>
       </c>
       <c r="DK15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL15" t="n">
         <v>-0</v>
       </c>
       <c r="DM15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO15" t="n">
-        <v>0.02819024879412505</v>
+        <v>-0.006240510592977514</v>
       </c>
       <c r="DP15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ15" t="n">
         <v>0</v>
       </c>
       <c r="DR15" t="n">
-        <v>0.006427089550697727</v>
+        <v>0.0470955959964233</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.01537158495180454</v>
+        <v>-0.01084738347153999</v>
       </c>
       <c r="DT15" t="n">
         <v>-0</v>
@@ -8777,46 +8777,46 @@
         <v>0</v>
       </c>
       <c r="DX15" t="n">
-        <v>-0.05509009402994478</v>
+        <v>-0.04168073698154528</v>
       </c>
       <c r="DY15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ15" t="n">
         <v>-0</v>
       </c>
       <c r="EA15" t="n">
-        <v>0.04832181087275859</v>
+        <v>0.03158566715415434</v>
       </c>
       <c r="EB15" t="n">
-        <v>-0.08093476203315494</v>
+        <v>0.003625771789836639</v>
       </c>
       <c r="EC15" t="n">
         <v>0</v>
       </c>
       <c r="ED15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG15" t="n">
-        <v>0.006044274492454821</v>
+        <v>0.04414202034847455</v>
       </c>
       <c r="EH15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.0322212431533716</v>
+        <v>-0.01216177437687673</v>
       </c>
       <c r="EK15" t="n">
-        <v>-0.1070273534060086</v>
+        <v>-0.03487252105683603</v>
       </c>
       <c r="EL15" t="n">
         <v>0</v>
@@ -8831,7 +8831,7 @@
         <v>0</v>
       </c>
       <c r="EP15" t="n">
-        <v>0.1663778337495811</v>
+        <v>0.07396722608138157</v>
       </c>
       <c r="EQ15" t="n">
         <v>0</v>
@@ -8840,10 +8840,10 @@
         <v>-0</v>
       </c>
       <c r="ES15" t="n">
-        <v>0.04905244398374226</v>
+        <v>0.02799099122088572</v>
       </c>
       <c r="ET15" t="n">
-        <v>-0.06585900017908174</v>
+        <v>0.138958518993039</v>
       </c>
       <c r="EU15" t="n">
         <v>0</v>
@@ -8852,85 +8852,85 @@
         <v>-0</v>
       </c>
       <c r="EW15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX15" t="n">
         <v>0</v>
       </c>
       <c r="EY15" t="n">
-        <v>0.07960054782456651</v>
+        <v>0.1133289702458214</v>
       </c>
       <c r="EZ15" t="n">
         <v>0</v>
       </c>
       <c r="FA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB15" t="n">
-        <v>0.04654217997812082</v>
+        <v>-0.02449817163226789</v>
       </c>
       <c r="FC15" t="n">
-        <v>-0.122348926020055</v>
+        <v>-0.08838630864922509</v>
       </c>
       <c r="FD15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE15" t="n">
         <v>-0</v>
       </c>
       <c r="FF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG15" t="n">
         <v>-0</v>
       </c>
       <c r="FH15" t="n">
-        <v>-0.05406957219163602</v>
+        <v>0.1029473352400945</v>
       </c>
       <c r="FI15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FK15" t="n">
-        <v>0.02807232655490399</v>
+        <v>-0.06837497192220082</v>
       </c>
       <c r="FL15" t="n">
-        <v>-0.1488221249007662</v>
+        <v>-0.07856723265769079</v>
       </c>
       <c r="FM15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN15" t="n">
         <v>-0</v>
       </c>
       <c r="FO15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ15" t="n">
-        <v>-0.009889436840908469</v>
+        <v>0.02970916870273703</v>
       </c>
       <c r="FR15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FT15" t="n">
-        <v>-0.02558915791179081</v>
+        <v>-0.01306313236407458</v>
       </c>
       <c r="FU15" t="n">
-        <v>-0.1846496305779978</v>
+        <v>-0.04832565089373789</v>
       </c>
       <c r="FV15" t="n">
         <v>0</v>
       </c>
       <c r="FW15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX15" t="n">
         <v>-0</v>
@@ -8939,10 +8939,10 @@
         <v>-0</v>
       </c>
       <c r="FZ15" t="n">
-        <v>0.06109323969379531</v>
+        <v>0.06826984852750882</v>
       </c>
       <c r="GA15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB15" t="n">
         <v>0</v>
@@ -8951,10 +8951,10 @@
         <v>-0</v>
       </c>
       <c r="GD15" t="n">
-        <v>-0.007123439085700193</v>
+        <v>0.02221660308821012</v>
       </c>
       <c r="GE15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF15" t="n">
         <v>0</v>
